--- a/results/Int Task Remove ACC 0.1/Rando_9_permute.xlsx
+++ b/results/Int Task Remove ACC 0.1/Rando_9_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6473252287864839</v>
+        <v>0.6263591812422158</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6473252287864839</v>
+        <v>0.624761737152759</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6456906915037635</v>
+        <v>0.6215340878323496</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6637688850381762</v>
+        <v>0.619983213299399</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6664436562516922</v>
+        <v>0.623359235392863</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6921373260410462</v>
+        <v>0.6502518005090161</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7010440244760925</v>
+        <v>0.649415985271024</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.70138300752694</v>
+        <v>0.6454223750473818</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7079539177993177</v>
+        <v>0.6503354632587859</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7086318839010126</v>
+        <v>0.5699474738723128</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6984063464558401</v>
+        <v>0.5930180863161315</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.695949802350138</v>
+        <v>0.5799358314831862</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.681633183516543</v>
+        <v>0.5378588834136568</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6883343260951968</v>
+        <v>0.5145751881734987</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6624267612497969</v>
+        <v>0.5231989494774463</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6858872583527373</v>
+        <v>0.5126439053446689</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6952907889749282</v>
+        <v>0.5071736069746033</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6974643959495316</v>
+        <v>0.5029341528131261</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6610085558022418</v>
+        <v>0.5025951697622787</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6262562950127254</v>
+        <v>0.5019310120755943</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6237626577137597</v>
+        <v>0.5115156766123355</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6234469594411653</v>
+        <v>0.5162614393242</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6042630096929658</v>
+        <v>0.5331648345697731</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6105734553527915</v>
+        <v>0.5236965939242973</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5976799155249906</v>
+        <v>0.5246626414685656</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5947403476471543</v>
+        <v>0.5688804353712027</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6747861049439541</v>
+        <v>0.5688804353712027</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6741685168137759</v>
+        <v>0.5694609303081172</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6741685168137759</v>
+        <v>0.5769564628797315</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6701153408783236</v>
+        <v>0.5951743650836627</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.70593464016895</v>
+        <v>0.5937580549087562</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.7066635078789192</v>
+        <v>0.5891468565549358</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.6626509449287918</v>
+        <v>0.6166044836735799</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6530844208588293</v>
+        <v>0.5469380516597173</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6619678345156225</v>
+        <v>0.5482336058915904</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.661169112470894</v>
+        <v>0.5570764065630585</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6033635674446309</v>
+        <v>0.5613719066442844</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.606391130124005</v>
+        <v>0.5650568581794553</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.629057237233985</v>
+        <v>0.5650568581794553</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6347698597498239</v>
+        <v>0.5876108734499377</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6227898413386039</v>
+        <v>0.582094005523366</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5946076785617588</v>
+        <v>0.5523972491471273</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.6020747820436454</v>
+        <v>0.5456546813234417</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5917103481886609</v>
+        <v>0.5495093951372719</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6242432447067743</v>
+        <v>0.5391587696972979</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.623602371798343</v>
+        <v>0.533131261168571</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6004480966047545</v>
+        <v>0.5216670276709807</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.599649374560026</v>
+        <v>0.4931150159744409</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5997511777765744</v>
+        <v>0.4931150159744409</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5974757675854226</v>
+        <v>0.4746287973141279</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5995933286402773</v>
+        <v>0.4827462500676883</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.6073019440082309</v>
+        <v>0.4670003249038826</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.6143187848594791</v>
+        <v>0.4649198570422917</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.6202721070016787</v>
+        <v>0.4670322737856717</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.6277719716250609</v>
+        <v>0.4665725347917908</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.661414956408729</v>
+        <v>0.4927768451832999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.6611639681594195</v>
+        <v>0.4645654410570206</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.6694487464125196</v>
+        <v>0.4621597985595928</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.686253858233606</v>
+        <v>0.4738249309579249</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.6547051497265393</v>
+        <v>0.4738249309579249</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6923693615638706</v>
+        <v>0.4687030920019494</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6961542210429414</v>
+        <v>0.4743588563383332</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.624988628364109</v>
+        <v>0.4764479883034602</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.627207992635512</v>
+        <v>0.4772699951264417</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.6267533979531055</v>
+        <v>0.4761322900308659</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.6319450912438404</v>
+        <v>0.4624245952239129</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.6320287539936102</v>
+        <v>0.4595367412140575</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.6437033627551849</v>
+        <v>0.4588354903341095</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.6374990523636758</v>
+        <v>0.4638555260735366</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6289640981209725</v>
+        <v>0.4664604429522933</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.63416526777495</v>
+        <v>0.496856825689067</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6243390913521416</v>
+        <v>0.4964065630584286</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6247151675962528</v>
+        <v>0.4992115665782206</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6068784859479071</v>
+        <v>0.4980971462608978</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5985807115395029</v>
+        <v>0.4955147019006877</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5979260302160611</v>
+        <v>0.4955147019006877</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5580719662099962</v>
+        <v>0.4989787187956896</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5503081171820003</v>
+        <v>0.499052905182217</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5523049222938214</v>
+        <v>0.4983145611090053</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5523049222938214</v>
+        <v>0.5003622678291005</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5342121080846916</v>
+        <v>0.5004830237721341</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5351359181242216</v>
+        <v>0.5017785780040072</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5313372502301402</v>
+        <v>0.5005201169653978</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4977340661720908</v>
+        <v>0.5001207559430335</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4997213949206693</v>
+        <v>0.4997817728921861</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4996610169491525</v>
+        <v>0.5009194779877619</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4993220338983051</v>
+        <v>0.5009798559592787</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4996610169491525</v>
+        <v>0.5009798559592787</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4996610169491525</v>
+        <v>0.4999025288352196</v>
       </c>
     </row>
   </sheetData>
